--- a/data/TIME.MI.xlsx
+++ b/data/TIME.MI.xlsx
@@ -30272,6 +30272,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1301">
+      <c r="A1301" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1301" t="n">
+        <v>15101</v>
+      </c>
+      <c r="C1301" t="n">
+        <v>0.395999997854233</v>
+      </c>
+      <c r="D1301" t="n">
+        <v>0.393999993801117</v>
+      </c>
+      <c r="E1301" t="n">
+        <v>0.393999993801117</v>
+      </c>
+      <c r="F1301" t="n">
+        <v>0.395999997854233</v>
+      </c>
+      <c r="G1301" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TIME.MI.xlsx
+++ b/data/TIME.MI.xlsx
@@ -30295,6 +30295,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1302">
+      <c r="A1302" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1302" t="n">
+        <v>89908</v>
+      </c>
+      <c r="C1302" t="n">
+        <v>0.398000001907349</v>
+      </c>
+      <c r="D1302" t="n">
+        <v>0.397000014781952</v>
+      </c>
+      <c r="E1302" t="n">
+        <v>0.398000001907349</v>
+      </c>
+      <c r="F1302" t="n">
+        <v>0.397000014781952</v>
+      </c>
+      <c r="G1302" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TIME.MI.xlsx
+++ b/data/TIME.MI.xlsx
@@ -30318,6 +30318,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1303">
+      <c r="A1303" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1303" t="n">
+        <v>39347</v>
+      </c>
+      <c r="C1303" t="n">
+        <v>0.400000005960464</v>
+      </c>
+      <c r="D1303" t="n">
+        <v>0.398000001907349</v>
+      </c>
+      <c r="E1303" t="n">
+        <v>0.398000001907349</v>
+      </c>
+      <c r="F1303" t="n">
+        <v>0.398000001907349</v>
+      </c>
+      <c r="G1303" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TIME.MI.xlsx
+++ b/data/TIME.MI.xlsx
@@ -30341,6 +30341,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1304">
+      <c r="A1304" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1304" t="n">
+        <v>15208</v>
+      </c>
+      <c r="C1304" t="n">
+        <v>0.398999989032745</v>
+      </c>
+      <c r="D1304" t="n">
+        <v>0.398999989032745</v>
+      </c>
+      <c r="E1304" t="n">
+        <v>0.398999989032745</v>
+      </c>
+      <c r="F1304" t="n">
+        <v>0.398999989032745</v>
+      </c>
+      <c r="G1304" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TIME.MI.xlsx
+++ b/data/TIME.MI.xlsx
@@ -30182,22 +30182,22 @@
     </row>
     <row r="1297">
       <c r="A1297" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1297" t="n">
-        <v>390989</v>
+        <v>28764</v>
       </c>
       <c r="C1297" t="n">
-        <v>0.409999996423721</v>
+        <v>0.400000005960464</v>
       </c>
       <c r="D1297" t="n">
-        <v>0.400000005960464</v>
+        <v>0.398000001907349</v>
       </c>
       <c r="E1297" t="n">
         <v>0.400000005960464</v>
       </c>
       <c r="F1297" t="n">
-        <v>0.400000005960464</v>
+        <v>0.398000001907349</v>
       </c>
       <c r="G1297" t="s">
         <v>7</v>
@@ -30205,19 +30205,19 @@
     </row>
     <row r="1298">
       <c r="A1298" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1298" t="n">
-        <v>142662</v>
+        <v>390989</v>
       </c>
       <c r="C1298" t="n">
-        <v>0.400999993085861</v>
+        <v>0.409999996423721</v>
       </c>
       <c r="D1298" t="n">
         <v>0.400000005960464</v>
       </c>
       <c r="E1298" t="n">
-        <v>0.400999993085861</v>
+        <v>0.400000005960464</v>
       </c>
       <c r="F1298" t="n">
         <v>0.400000005960464</v>
@@ -30228,22 +30228,22 @@
     </row>
     <row r="1299">
       <c r="A1299" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1299" t="n">
-        <v>28200</v>
+        <v>142662</v>
       </c>
       <c r="C1299" t="n">
-        <v>0.398000001907349</v>
+        <v>0.400999993085861</v>
       </c>
       <c r="D1299" t="n">
-        <v>0.395999997854233</v>
+        <v>0.400000005960464</v>
       </c>
       <c r="E1299" t="n">
-        <v>0.398000001907349</v>
+        <v>0.400999993085861</v>
       </c>
       <c r="F1299" t="n">
-        <v>0.395999997854233</v>
+        <v>0.400000005960464</v>
       </c>
       <c r="G1299" t="s">
         <v>7</v>
@@ -30251,22 +30251,22 @@
     </row>
     <row r="1300">
       <c r="A1300" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1300" t="n">
-        <v>6103</v>
+        <v>28200</v>
       </c>
       <c r="C1300" t="n">
-        <v>0.395000010728836</v>
+        <v>0.398000001907349</v>
       </c>
       <c r="D1300" t="n">
-        <v>0.391999989748001</v>
+        <v>0.395999997854233</v>
       </c>
       <c r="E1300" t="n">
-        <v>0.391999989748001</v>
+        <v>0.398000001907349</v>
       </c>
       <c r="F1300" t="n">
-        <v>0.395000010728836</v>
+        <v>0.395999997854233</v>
       </c>
       <c r="G1300" t="s">
         <v>7</v>
@@ -30274,22 +30274,22 @@
     </row>
     <row r="1301">
       <c r="A1301" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1301" t="n">
-        <v>15101</v>
+        <v>6103</v>
       </c>
       <c r="C1301" t="n">
-        <v>0.395999997854233</v>
+        <v>0.395000010728836</v>
       </c>
       <c r="D1301" t="n">
-        <v>0.393999993801117</v>
+        <v>0.391999989748001</v>
       </c>
       <c r="E1301" t="n">
-        <v>0.393999993801117</v>
+        <v>0.391999989748001</v>
       </c>
       <c r="F1301" t="n">
-        <v>0.395999997854233</v>
+        <v>0.395000010728836</v>
       </c>
       <c r="G1301" t="s">
         <v>7</v>
@@ -30297,22 +30297,22 @@
     </row>
     <row r="1302">
       <c r="A1302" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1302" t="n">
-        <v>89908</v>
+        <v>15101</v>
       </c>
       <c r="C1302" t="n">
-        <v>0.398000001907349</v>
+        <v>0.395999997854233</v>
       </c>
       <c r="D1302" t="n">
-        <v>0.397000014781952</v>
+        <v>0.393999993801117</v>
       </c>
       <c r="E1302" t="n">
-        <v>0.398000001907349</v>
+        <v>0.393999993801117</v>
       </c>
       <c r="F1302" t="n">
-        <v>0.397000014781952</v>
+        <v>0.395999997854233</v>
       </c>
       <c r="G1302" t="s">
         <v>7</v>
@@ -30320,22 +30320,22 @@
     </row>
     <row r="1303">
       <c r="A1303" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1303" t="n">
-        <v>39347</v>
+        <v>89908</v>
       </c>
       <c r="C1303" t="n">
-        <v>0.400000005960464</v>
+        <v>0.398000001907349</v>
       </c>
       <c r="D1303" t="n">
-        <v>0.398000001907349</v>
+        <v>0.397000014781952</v>
       </c>
       <c r="E1303" t="n">
         <v>0.398000001907349</v>
       </c>
       <c r="F1303" t="n">
-        <v>0.398000001907349</v>
+        <v>0.397000014781952</v>
       </c>
       <c r="G1303" t="s">
         <v>7</v>
@@ -30343,22 +30343,22 @@
     </row>
     <row r="1304">
       <c r="A1304" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1304" t="n">
-        <v>15208</v>
+        <v>39347</v>
       </c>
       <c r="C1304" t="n">
-        <v>0.398999989032745</v>
+        <v>0.400000005960464</v>
       </c>
       <c r="D1304" t="n">
-        <v>0.398999989032745</v>
+        <v>0.398000001907349</v>
       </c>
       <c r="E1304" t="n">
-        <v>0.398999989032745</v>
+        <v>0.398000001907349</v>
       </c>
       <c r="F1304" t="n">
-        <v>0.398999989032745</v>
+        <v>0.398000001907349</v>
       </c>
       <c r="G1304" t="s">
         <v>7</v>

--- a/data/TIME.MI.xlsx
+++ b/data/TIME.MI.xlsx
@@ -30364,6 +30364,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1305">
+      <c r="A1305" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1305" t="n">
+        <v>15208</v>
+      </c>
+      <c r="C1305" t="n">
+        <v>0.398999989032745</v>
+      </c>
+      <c r="D1305" t="n">
+        <v>0.398999989032745</v>
+      </c>
+      <c r="E1305" t="n">
+        <v>0.398999989032745</v>
+      </c>
+      <c r="F1305" t="n">
+        <v>0.398999989032745</v>
+      </c>
+      <c r="G1305" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1306" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1306" t="n">
+        <v>0.398999989032745</v>
+      </c>
+      <c r="D1306" t="n">
+        <v>0.398999989032745</v>
+      </c>
+      <c r="E1306" t="n">
+        <v>0.398999989032745</v>
+      </c>
+      <c r="F1306" t="n">
+        <v>0.398999989032745</v>
+      </c>
+      <c r="G1306" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TIME.MI.xlsx
+++ b/data/TIME.MI.xlsx
@@ -30410,6 +30410,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1307">
+      <c r="A1307" s="1" t="n">
+        <v>46286.2916666667</v>
+      </c>
+      <c r="B1307" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1307" t="n">
+        <v>0.398999989032745</v>
+      </c>
+      <c r="D1307" t="n">
+        <v>0.398999989032745</v>
+      </c>
+      <c r="E1307" t="n">
+        <v>0.398999989032745</v>
+      </c>
+      <c r="F1307" t="n">
+        <v>0.398999989032745</v>
+      </c>
+      <c r="G1307" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TIME.MI.xlsx
+++ b/data/TIME.MI.xlsx
@@ -30433,6 +30433,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1308">
+      <c r="A1308" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1308" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1308" t="n">
+        <v>0.398999989032745</v>
+      </c>
+      <c r="D1308" t="n">
+        <v>0.398999989032745</v>
+      </c>
+      <c r="E1308" t="n">
+        <v>0.398999989032745</v>
+      </c>
+      <c r="F1308" t="n">
+        <v>0.398999989032745</v>
+      </c>
+      <c r="G1308" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
